--- a/data/trans_dic/P32-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensa que debería beber menos</t>
+          <t>Población que piensa que debería beber menos (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,46</t>
+          <t>2,98; 8,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,04; 14,44</t>
+          <t>7,25; 14,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 11,47</t>
+          <t>4,31; 11,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,07; 17,14</t>
+          <t>2,22; 18,22</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,28</t>
+          <t>1,02; 6,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,45</t>
+          <t>1,06; 5,88</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 11,64</t>
+          <t>4,27; 11,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 15,25</t>
+          <t>1,69; 14,6</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,69</t>
+          <t>2,56; 6,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 10,23</t>
+          <t>5,31; 10,2</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,08; 10,41</t>
+          <t>5,06; 10,59</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,84; 13,84</t>
+          <t>2,63; 13,27</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 5,04</t>
+          <t>1,83; 4,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,78; 10,94</t>
+          <t>5,62; 10,97</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,55; 10,12</t>
+          <t>4,5; 10,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,52; 12,48</t>
+          <t>3,7; 12,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,53</t>
+          <t>0,0; 5,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 8,3</t>
+          <t>1,74; 8,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 6,69</t>
+          <t>1,98; 6,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 8,28</t>
+          <t>0,89; 9,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,83</t>
+          <t>1,49; 3,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 8,9</t>
+          <t>5,02; 8,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,96; 7,86</t>
+          <t>4,02; 8,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 9,25</t>
+          <t>3,29; 9,25</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,72</t>
+          <t>0,46; 2,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 7,37</t>
+          <t>2,96; 7,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,8; 5,45</t>
+          <t>1,85; 5,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 10,2</t>
+          <t>3,77; 9,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 3,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 6,4</t>
+          <t>1,29; 6,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,97</t>
+          <t>0,33; 2,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,91</t>
+          <t>0,78; 5,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,39</t>
+          <t>0,49; 2,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,95</t>
+          <t>2,99; 6,31</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,9</t>
+          <t>1,39; 3,64</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 7,32</t>
+          <t>3,05; 7,44</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,64</t>
+          <t>0,34; 3,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 10,71</t>
+          <t>4,93; 10,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,35; 9,67</t>
+          <t>4,31; 9,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,59; 6,95</t>
+          <t>2,66; 7,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,17</t>
+          <t>0,0; 4,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,01</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 6,55</t>
+          <t>1,62; 6,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,28</t>
+          <t>0,83; 3,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,06</t>
+          <t>0,47; 2,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 7,07</t>
+          <t>3,19; 7,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 7,3</t>
+          <t>3,72; 7,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 5,11</t>
+          <t>2,23; 5,24</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 9,6</t>
+          <t>2,99; 10,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 7,35</t>
+          <t>1,63; 7,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,33; 9,53</t>
+          <t>3,1; 9,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,4; 13,0</t>
+          <t>6,14; 13,01</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,09</t>
+          <t>0,0; 9,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,77</t>
+          <t>0,0; 5,93</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 8,76</t>
+          <t>0,85; 8,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,48</t>
+          <t>1,72; 6,56</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,19; 7,32</t>
+          <t>2,17; 7,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,14</t>
+          <t>1,12; 5,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,79</t>
+          <t>2,88; 7,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,41; 10,56</t>
+          <t>5,48; 9,99</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,79</t>
+          <t>0,0; 6,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,21; 12,49</t>
+          <t>3,2; 12,5</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,02</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,63; 9,55</t>
+          <t>3,75; 9,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,96</t>
+          <t>0,0; 7,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,37</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,12</t>
+          <t>0,0; 5,58</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,93; 9,42</t>
+          <t>1,92; 9,2</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,41</t>
+          <t>0,39; 3,5</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,69; 5,62</t>
+          <t>0,7; 5,51</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,98</t>
+          <t>0,0; 6,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,42</t>
+          <t>0,0; 11,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,74</t>
+          <t>0,0; 9,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,9</t>
+          <t>0,0; 4,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,67</t>
+          <t>0,0; 8,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,57</t>
+          <t>0,0; 6,32</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,25</t>
+          <t>0,0; 11,05</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,91</t>
+          <t>0,0; 7,06</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,73</t>
+          <t>0,43; 4,08</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,7</t>
+          <t>2,07; 3,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,92</t>
+          <t>5,66; 7,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,31; 6,45</t>
+          <t>4,28; 6,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,85; 7,64</t>
+          <t>4,94; 7,71</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,54</t>
+          <t>0,79; 2,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,34</t>
+          <t>1,32; 3,29</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,51</t>
+          <t>2,32; 4,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,67</t>
+          <t>1,22; 3,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,96</t>
+          <t>1,83; 3,0</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,42; 6,13</t>
+          <t>4,33; 6,06</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,78; 5,39</t>
+          <t>3,73; 5,27</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,58; 5,76</t>
+          <t>3,58; 5,78</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que piensa que debería beber menos</t>
+          <t>Población que piensa que debería beber menos (tasa de respuesta: 99,75%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8158; 23742</t>
+          <t>8366; 23249</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19837; 40697</t>
+          <t>20444; 41540</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11093; 29257</t>
+          <t>10990; 30470</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3515; 29117</t>
+          <t>3765; 30950</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1884; 11642</t>
+          <t>1887; 12891</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1872; 11900</t>
+          <t>1960; 10853</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6382; 19981</t>
+          <t>7332; 20421</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1670; 15375</t>
+          <t>1709; 14729</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12344; 31167</t>
+          <t>11943; 29471</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24831; 47718</t>
+          <t>24780; 47564</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21701; 44411</t>
+          <t>21604; 45181</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7680; 37466</t>
+          <t>7107; 35929</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9167; 25314</t>
+          <t>9164; 24848</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26974; 51105</t>
+          <t>26226; 51222</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16673; 37081</t>
+          <t>16487; 37974</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8099; 28725</t>
+          <t>8521; 29036</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 9895</t>
+          <t>0; 11119</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3672; 17715</t>
+          <t>3723; 17107</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3830; 15085</t>
+          <t>4464; 15647</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1482; 11779</t>
+          <t>1262; 12818</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10446; 27566</t>
+          <t>10696; 27207</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>33257; 60540</t>
+          <t>34164; 61149</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23472; 46569</t>
+          <t>23811; 47478</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11905; 34461</t>
+          <t>12238; 34441</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1852; 10931</t>
+          <t>1841; 11454</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12945; 31477</t>
+          <t>12624; 30773</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7776; 23505</t>
+          <t>7970; 23948</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10516; 28777</t>
+          <t>10634; 27916</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 6708</t>
+          <t>0; 7490</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3084; 15644</t>
+          <t>3147; 16656</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>818; 7407</t>
+          <t>821; 7447</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1294; 7402</t>
+          <t>1178; 7789</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2934; 14984</t>
+          <t>3068; 13474</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>19201; 39978</t>
+          <t>20084; 42336</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10012; 26508</t>
+          <t>9446; 24746</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13859; 31683</t>
+          <t>13203; 32195</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1072; 11423</t>
+          <t>1067; 10505</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19612; 42198</t>
+          <t>19447; 42871</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17013; 37786</t>
+          <t>16841; 37310</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8912; 23912</t>
+          <t>9145; 25537</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7501</t>
+          <t>0; 7127</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2176</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4341; 17369</t>
+          <t>4296; 16745</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1538; 8205</t>
+          <t>1593; 7549</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2147; 14020</t>
+          <t>2165; 13305</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19439; 43098</t>
+          <t>19439; 43435</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23080; 47887</t>
+          <t>24429; 48822</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11552; 27376</t>
+          <t>11948; 28077</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>4670; 17283</t>
+          <t>5388; 18104</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3183; 17030</t>
+          <t>3789; 17134</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9521; 27200</t>
+          <t>8860; 26413</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16826; 34203</t>
+          <t>16158; 34226</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5346</t>
+          <t>0; 7037</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 4191</t>
+          <t>0; 6592</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1117; 11440</t>
+          <t>1107; 10932</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2218; 8737</t>
+          <t>2317; 8834</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5593; 18704</t>
+          <t>5538; 19193</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4072; 17628</t>
+          <t>3858; 17968</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12132; 32415</t>
+          <t>11992; 32106</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21522; 42020</t>
+          <t>21779; 39719</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 10117</t>
+          <t>0; 8830</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4928; 19158</t>
+          <t>4904; 19166</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 7062</t>
+          <t>0; 6530</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6888; 18137</t>
+          <t>7129; 17884</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1752</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2114</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5382</t>
+          <t>0; 5299</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 6632</t>
+          <t>0; 6436</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 8158</t>
+          <t>0; 8880</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4064; 19851</t>
+          <t>4045; 19392</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>955; 8286</t>
+          <t>950; 8519</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3227; 26387</t>
+          <t>3303; 25876</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5108</t>
+          <t>0; 5062</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 10623</t>
+          <t>0; 9716</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 8344</t>
+          <t>0; 8593</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4897</t>
+          <t>0; 4406</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2083</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2015</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 2679</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 2320</t>
+          <t>0; 2242</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4996</t>
+          <t>0; 5670</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 12360</t>
+          <t>0; 12142</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 9127</t>
+          <t>0; 9318</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>543; 4726</t>
+          <t>551; 5168</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>39191; 69535</t>
+          <t>38924; 66093</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>114844; 161660</t>
+          <t>115514; 162242</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>86191; 129082</t>
+          <t>85564; 128607</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>76577; 120635</t>
+          <t>77979; 121734</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6959; 22689</t>
+          <t>7108; 22856</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14266; 35088</t>
+          <t>13863; 34593</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>27059; 51661</t>
+          <t>26546; 51518</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>12219; 37688</t>
+          <t>12493; 37468</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>50238; 82102</t>
+          <t>50788; 83364</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>136494; 189385</t>
+          <t>133873; 187440</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>118964; 169567</t>
+          <t>117227; 165883</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>93260; 150209</t>
+          <t>93197; 150627</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 8,28</t>
+          <t>2,97; 8,83</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,25; 14,74</t>
+          <t>7,41; 15,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 11,94</t>
+          <t>4,46; 11,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,22; 18,22</t>
+          <t>2,95; 17,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,95</t>
+          <t>1,01; 6,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,06; 5,88</t>
+          <t>1,07; 5,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,27; 11,9</t>
+          <t>3,82; 12,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 14,6</t>
+          <t>3,07; 17,79</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 6,32</t>
+          <t>2,5; 6,25</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,31; 10,2</t>
+          <t>5,21; 10,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,06; 10,59</t>
+          <t>5,15; 10,32</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,63; 13,27</t>
+          <t>4,38; 14,93</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,95</t>
+          <t>1,72; 4,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,62; 10,97</t>
+          <t>5,55; 10,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,5; 10,36</t>
+          <t>4,62; 10,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 12,62</t>
+          <t>3,97; 12,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,09</t>
+          <t>0,0; 4,78</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 8,01</t>
+          <t>1,82; 7,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 6,94</t>
+          <t>1,8; 7,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 9,01</t>
+          <t>0,92; 8,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,78</t>
+          <t>1,44; 4,04</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,99</t>
+          <t>4,95; 9,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4,02; 8,02</t>
+          <t>3,98; 7,69</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 9,25</t>
+          <t>3,55; 9,1</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,85</t>
+          <t>0,44; 2,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,96; 7,21</t>
+          <t>2,94; 7,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,55</t>
+          <t>1,8; 5,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,77; 9,89</t>
+          <t>4,54; 10,85</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,34</t>
+          <t>0,0; 3,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,82</t>
+          <t>1,59; 6,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,99</t>
+          <t>0,33; 3,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,16</t>
+          <t>0,56; 4,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,15</t>
+          <t>0,46; 2,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,31</t>
+          <t>2,87; 6,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,39; 3,64</t>
+          <t>1,39; 3,94</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 7,44</t>
+          <t>3,34; 7,55</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,35</t>
+          <t>0,34; 3,36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,93; 10,88</t>
+          <t>5,04; 10,82</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,31; 9,55</t>
+          <t>4,25; 9,65</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,42</t>
+          <t>2,72; 7,11</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1167,32 +1167,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,31</t>
+          <t>1,26; 6,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,94</t>
+          <t>0,96; 4,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,9</t>
+          <t>0,49; 3,18</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3,19; 7,13</t>
+          <t>3,08; 7,07</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,44</t>
+          <t>3,54; 7,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,24</t>
+          <t>2,37; 5,56</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,99; 10,05</t>
+          <t>2,95; 10,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 7,39</t>
+          <t>1,66; 7,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,1; 9,25</t>
+          <t>3,1; 9,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6,14; 13,01</t>
+          <t>6,23; 12,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,33</t>
+          <t>0,0; 5,58</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,93</t>
+          <t>0,0; 4,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 8,37</t>
+          <t>0,85; 8,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,72; 6,56</t>
+          <t>1,66; 6,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,51</t>
+          <t>2,14; 7,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,12; 5,24</t>
+          <t>1,17; 5,25</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 7,71</t>
+          <t>3,06; 7,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,48; 9,99</t>
+          <t>5,07; 9,7</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,8</t>
+          <t>0,0; 7,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,2; 12,5</t>
+          <t>2,71; 12,81</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,75; 9,41</t>
+          <t>3,83; 9,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1447,32 +1447,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,84</t>
+          <t>0,0; 8,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,58; 6,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,58</t>
+          <t>0,0; 5,7</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,92; 9,2</t>
+          <t>1,91; 9,1</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,5</t>
+          <t>0,4; 3,67</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 5,51</t>
+          <t>3,19; 7,66</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,75%</t>
         </is>
       </c>
     </row>
@@ -1557,22 +1557,22 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,92</t>
+          <t>0,0; 6,93</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,36</t>
+          <t>0,0; 13,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,0</t>
+          <t>0,0; 8,13</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,4</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1592,27 +1592,27 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,38</t>
+          <t>0,0; 12,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,32</t>
+          <t>0,0; 6,16</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,05</t>
+          <t>0,0; 10,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,06</t>
+          <t>0,0; 6,13</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,08</t>
+          <t>0,48; 4,51</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,51</t>
+          <t>2,08; 3,61</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,66; 7,95</t>
+          <t>5,61; 8,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4,28; 6,43</t>
+          <t>4,32; 6,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,94; 7,71</t>
+          <t>5,2; 8,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,55</t>
+          <t>0,8; 2,49</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,29</t>
+          <t>1,31; 3,41</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,49</t>
+          <t>2,39; 4,53</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,22; 3,65</t>
+          <t>2,4; 5,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,0</t>
+          <t>1,8; 2,94</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,33; 6,06</t>
+          <t>4,4; 6,01</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,73; 5,27</t>
+          <t>3,84; 5,34</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,58; 5,78</t>
+          <t>4,59; 6,54</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11362</t>
+          <t>13348</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5898</t>
+          <t>9549</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17260</t>
+          <t>22896</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8366; 23249</t>
+          <t>8349; 24777</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20444; 41540</t>
+          <t>20874; 42387</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>10990; 30470</t>
+          <t>11392; 29262</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3765; 30950</t>
+          <t>4905; 29754</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1887; 12891</t>
+          <t>1870; 12804</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1960; 10853</t>
+          <t>1975; 10749</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7332; 20421</t>
+          <t>6560; 20663</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1709; 14729</t>
+          <t>3461; 20076</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>11943; 29471</t>
+          <t>11642; 29134</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24780; 47564</t>
+          <t>24283; 47178</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21604; 45181</t>
+          <t>21971; 44030</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7107; 35929</t>
+          <t>12215; 41657</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15879</t>
+          <t>18256</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5123</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>21001</t>
+          <t>23623</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9164; 24848</t>
+          <t>8636; 23479</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26226; 51222</t>
+          <t>25902; 50378</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16487; 37974</t>
+          <t>16943; 36789</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8521; 29036</t>
+          <t>9900; 30740</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 11119</t>
+          <t>0; 10437</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3723; 17107</t>
+          <t>3886; 16280</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4464; 15647</t>
+          <t>4065; 15822</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1262; 12818</t>
+          <t>1401; 12644</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10696; 27207</t>
+          <t>10350; 29088</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>34164; 61149</t>
+          <t>33648; 62260</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23811; 47478</t>
+          <t>23545; 45525</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12238; 34441</t>
+          <t>14302; 36637</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17639</t>
+          <t>22005</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3360</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>20999</t>
+          <t>25609</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1841; 11454</t>
+          <t>1772; 10713</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12624; 30773</t>
+          <t>12545; 30535</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7970; 23948</t>
+          <t>7782; 21591</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10634; 27916</t>
+          <t>14193; 33930</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 7490</t>
+          <t>0; 6860</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3147; 16656</t>
+          <t>3880; 16856</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>821; 7447</t>
+          <t>826; 7687</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1178; 7789</t>
+          <t>960; 7778</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3068; 13474</t>
+          <t>2887; 13468</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20084; 42336</t>
+          <t>19294; 40533</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9446; 24746</t>
+          <t>9479; 26834</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>13203; 32195</t>
+          <t>16143; 36463</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15219</t>
+          <t>16092</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>4843</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18864</t>
+          <t>20935</t>
         </is>
       </c>
     </row>
@@ -2692,27 +2692,27 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1067; 10505</t>
+          <t>1063; 10547</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19447; 42871</t>
+          <t>19877; 42624</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16841; 37310</t>
+          <t>16592; 37681</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9145; 25537</t>
+          <t>9616; 25161</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 7127</t>
+          <t>0; 7131</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2722,32 +2722,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4296; 16745</t>
+          <t>3329; 16081</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1593; 7549</t>
+          <t>2040; 9553</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2165; 13305</t>
+          <t>2237; 14602</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19439; 43435</t>
+          <t>18769; 43113</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24429; 48822</t>
+          <t>23189; 47314</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11948; 28077</t>
+          <t>13390; 31437</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24697</t>
+          <t>24866</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>5082</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>29420</t>
+          <t>29948</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>5388; 18104</t>
+          <t>5321; 18837</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3789; 17134</t>
+          <t>3850; 18233</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8860; 26413</t>
+          <t>8863; 25866</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16158; 34226</t>
+          <t>17471; 34861</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 7037</t>
+          <t>0; 4206</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 6592</t>
+          <t>0; 5521</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1107; 10932</t>
+          <t>1113; 11142</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>2317; 8834</t>
+          <t>2450; 9908</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5538; 19193</t>
+          <t>5470; 18125</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3858; 17968</t>
+          <t>4005; 17992</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11992; 32106</t>
+          <t>12739; 32733</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21779; 39719</t>
+          <t>21712; 41573</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11688</t>
+          <t>13265</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1695</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12861</t>
+          <t>14959</t>
         </is>
       </c>
     </row>
@@ -3108,22 +3108,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 8830</t>
+          <t>0; 9179</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4904; 19166</t>
+          <t>4159; 19649</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 6530</t>
+          <t>0; 6907</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7129; 17884</t>
+          <t>7956; 20008</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3138,32 +3138,32 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5299</t>
+          <t>0; 5637</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 6436</t>
+          <t>462; 5392</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 8880</t>
+          <t>0; 9072</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4045; 19392</t>
+          <t>4034; 19194</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>950; 8519</t>
+          <t>966; 8923</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3303; 25876</t>
+          <t>9182; 22022</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>1354</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>564</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1816</t>
+          <t>2462</t>
         </is>
       </c>
     </row>
@@ -3316,22 +3316,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5062</t>
+          <t>0; 5071</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 9716</t>
+          <t>0; 11417</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 8593</t>
+          <t>0; 7755</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4406</t>
+          <t>0; 4618</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3351,27 +3351,27 @@
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 2242</t>
+          <t>0; 3985</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5670</t>
+          <t>0; 5525</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 12142</t>
+          <t>0; 11099</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>0; 9318</t>
+          <t>0; 8086</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>551; 5168</t>
+          <t>670; 6337</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>97735</t>
+          <t>109186</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>24487</t>
+          <t>31247</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>122222</t>
+          <t>140433</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>38924; 66093</t>
+          <t>39033; 67920</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>115514; 162242</t>
+          <t>114463; 163599</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>85564; 128607</t>
+          <t>86421; 127534</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>77979; 121734</t>
+          <t>87427; 134739</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>7108; 22856</t>
+          <t>7166; 22250</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13863; 34593</t>
+          <t>13739; 35819</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26546; 51518</t>
+          <t>27421; 51923</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>12493; 37468</t>
+          <t>21744; 45524</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>50788; 83364</t>
+          <t>49996; 81576</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>133873; 187440</t>
+          <t>135889; 185844</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>117227; 165883</t>
+          <t>120909; 168154</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>93197; 150627</t>
+          <t>118684; 169199</t>
         </is>
       </c>
     </row>
